--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/26. admnistrative_unit.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/26. admnistrative_unit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\2. location_area [21,24-28,6]\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\dml\city location institution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB10446-B5DC-4EE4-9764-7AC2016287BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E524391B-3AFB-428B-BAB4-F5330457636C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12204" yWindow="840" windowWidth="4560" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12536,10 +12536,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1668"/>
+  <dimension ref="A1:H1669"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
     <col min="2" max="2" width="7.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.109375" customWidth="1"/>
     <col min="4" max="4" width="7.88671875" customWidth="1"/>
@@ -12912,7 +12912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>92</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>106</v>
       </c>
@@ -13354,7 +13354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>138</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>27</v>
       </c>
@@ -13978,7 +13978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>32</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>41</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>46</v>
       </c>
@@ -14420,7 +14420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>197</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>205</v>
       </c>
@@ -15512,7 +15512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>270</v>
       </c>
@@ -15772,7 +15772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>284</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>287</v>
       </c>
@@ -16448,7 +16448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>320</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>452</v>
       </c>
@@ -17878,7 +17878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>457</v>
       </c>
@@ -17982,7 +17982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>468</v>
       </c>
@@ -18190,7 +18190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>490</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>646</v>
       </c>
@@ -20140,7 +20140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>3910</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>3913</v>
       </c>
@@ -21076,7 +21076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>766</v>
       </c>
@@ -21154,7 +21154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>773</v>
       </c>
@@ -21206,7 +21206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>778</v>
       </c>
@@ -22454,7 +22454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>3934</v>
       </c>
@@ -22532,7 +22532,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>3937</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>931</v>
       </c>
@@ -22922,7 +22922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>936</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>939</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>972</v>
       </c>
@@ -23442,7 +23442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>984</v>
       </c>
@@ -23520,7 +23520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>992</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>1001</v>
       </c>
@@ -23650,7 +23650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>1005</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>1007</v>
       </c>
@@ -23910,7 +23910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>1028</v>
       </c>
@@ -23962,7 +23962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>1033</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>1035</v>
       </c>
@@ -25964,7 +25964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>1239</v>
       </c>
@@ -28018,7 +28018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A596" s="2" t="s">
         <v>1447</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="622" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A622" s="2" t="s">
         <v>1518</v>
       </c>
@@ -28902,7 +28902,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
         <v>1541</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A643" s="2" t="s">
         <v>1572</v>
       </c>
@@ -29292,7 +29292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
         <v>1577</v>
       </c>
@@ -29526,7 +29526,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A654" s="2" t="s">
         <v>1600</v>
       </c>
@@ -29708,7 +29708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
         <v>3959</v>
       </c>
@@ -29760,7 +29760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A663" s="2" t="s">
         <v>3961</v>
       </c>
@@ -29994,7 +29994,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
         <v>1630</v>
       </c>
@@ -30020,7 +30020,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
         <v>1633</v>
       </c>
@@ -30072,7 +30072,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
         <v>1637</v>
       </c>
@@ -30384,7 +30384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
         <v>1664</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
         <v>1667</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
         <v>1670</v>
       </c>
@@ -30462,7 +30462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
         <v>1673</v>
       </c>
@@ -30488,7 +30488,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
         <v>1675</v>
       </c>
@@ -30514,7 +30514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
         <v>1678</v>
       </c>
@@ -30644,7 +30644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
         <v>1692</v>
       </c>
@@ -31398,7 +31398,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A726" s="2" t="s">
         <v>1755</v>
       </c>
@@ -31476,7 +31476,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A729" s="2" t="s">
         <v>1764</v>
       </c>
@@ -32152,7 +32152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A755" s="2" t="s">
         <v>1826</v>
       </c>
@@ -32178,7 +32178,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A756" s="2" t="s">
         <v>1829</v>
       </c>
@@ -33504,7 +33504,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A807" s="2" t="s">
         <v>1953</v>
       </c>
@@ -34908,7 +34908,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A861" s="2" t="s">
         <v>2080</v>
       </c>
@@ -35012,7 +35012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A865" s="2" t="s">
         <v>2088</v>
       </c>
@@ -35090,7 +35090,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A868" s="2" t="s">
         <v>2095</v>
       </c>
@@ -35142,7 +35142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A870" s="2" t="s">
         <v>3974</v>
       </c>
@@ -35428,7 +35428,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
         <v>2125</v>
       </c>
@@ -35480,7 +35480,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A883" s="2" t="s">
         <v>2129</v>
       </c>
@@ -36494,7 +36494,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="922" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
         <v>2217</v>
       </c>
@@ -39016,7 +39016,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1019" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1019" s="2" t="s">
         <v>2422</v>
       </c>
@@ -39276,7 +39276,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1029" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1029" s="2" t="s">
         <v>2445</v>
       </c>
@@ -39302,7 +39302,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1030" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1030" s="2" t="s">
         <v>2448</v>
       </c>
@@ -39354,7 +39354,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1032" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1032" s="2" t="s">
         <v>2454</v>
       </c>
@@ -39432,7 +39432,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1035" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1035" s="2" t="s">
         <v>2460</v>
       </c>
@@ -39588,7 +39588,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1041" s="2" t="s">
         <v>2475</v>
       </c>
@@ -40680,7 +40680,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1083" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1083" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1083" s="2" t="s">
         <v>2573</v>
       </c>
@@ -40732,7 +40732,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1085" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1085" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1085" s="2" t="s">
         <v>2577</v>
       </c>
@@ -40810,7 +40810,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1088" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1088" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1088" s="2" t="s">
         <v>2584</v>
       </c>
@@ -41200,7 +41200,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1103" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1103" s="2" t="s">
         <v>2616</v>
       </c>
@@ -41434,7 +41434,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1112" s="2" t="s">
         <v>2635</v>
       </c>
@@ -44710,7 +44710,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="1238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1238" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1238" s="2" t="s">
         <v>2916</v>
       </c>
@@ -45646,7 +45646,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1274" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1274" s="2" t="s">
         <v>3015</v>
       </c>
@@ -45672,7 +45672,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1275" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1275" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1275" s="2" t="s">
         <v>3017</v>
       </c>
@@ -45698,7 +45698,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1276" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1276" s="2" t="s">
         <v>3020</v>
       </c>
@@ -45724,7 +45724,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1277" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1277" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1277" s="2" t="s">
         <v>3023</v>
       </c>
@@ -45750,7 +45750,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1278" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1278" s="2" t="s">
         <v>3026</v>
       </c>
@@ -45776,7 +45776,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1279" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1279" s="2" t="s">
         <v>3029</v>
       </c>
@@ -45802,7 +45802,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1280" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1280" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1280" s="2" t="s">
         <v>3032</v>
       </c>
@@ -45828,7 +45828,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1281" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1281" s="2" t="s">
         <v>3035</v>
       </c>
@@ -45880,7 +45880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1283" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1283" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1283" s="2" t="s">
         <v>3039</v>
       </c>
@@ -45906,7 +45906,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1284" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1284" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1284" s="2" t="s">
         <v>3041</v>
       </c>
@@ -45984,7 +45984,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1287" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1287" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1287" s="2" t="s">
         <v>3048</v>
       </c>
@@ -46010,7 +46010,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1288" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1288" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1288" s="2" t="s">
         <v>3051</v>
       </c>
@@ -46036,7 +46036,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="1289" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1289" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1289" s="2" t="s">
         <v>3053</v>
       </c>
@@ -46608,7 +46608,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="1311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1311" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1311" s="2" t="s">
         <v>3986</v>
       </c>
@@ -47440,7 +47440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="1343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1343" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1343" s="2" t="s">
         <v>3192</v>
       </c>
@@ -47492,7 +47492,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="1345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1345" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1345" s="2" t="s">
         <v>3196</v>
       </c>
@@ -47622,7 +47622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="1350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1350" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1350" s="2" t="s">
         <v>3208</v>
       </c>
@@ -47648,7 +47648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="1351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1351" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1351" s="2" t="s">
         <v>3211</v>
       </c>
@@ -50066,7 +50066,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="1444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1444" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1444" s="2" t="s">
         <v>3988</v>
       </c>
@@ -50092,7 +50092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="1445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1445" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1445" s="2" t="s">
         <v>3408</v>
       </c>
@@ -50586,7 +50586,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1464" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1464" s="2" t="s">
         <v>3455</v>
       </c>
@@ -50638,7 +50638,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="1466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1466" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1466" s="2" t="s">
         <v>3461</v>
       </c>
@@ -52068,7 +52068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="1521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1521" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1521" s="2" t="s">
         <v>3594</v>
       </c>
@@ -52224,7 +52224,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="1527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1527" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1527" s="2" t="s">
         <v>3609</v>
       </c>
@@ -53316,7 +53316,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="1569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1569" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1569" s="2" t="s">
         <v>3699</v>
       </c>
@@ -53342,7 +53342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="1570" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1570" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1570" s="2" t="s">
         <v>3701</v>
       </c>
@@ -53862,7 +53862,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="1590" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1590" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1590" s="2" t="s">
         <v>3743</v>
       </c>
@@ -54226,7 +54226,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="1604" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1604" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1604" s="2" t="s">
         <v>3774</v>
       </c>
@@ -54434,7 +54434,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="1612" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1612" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1612" s="2" t="s">
         <v>3789</v>
       </c>
@@ -54460,7 +54460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="1613" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1613" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1613" s="2" t="s">
         <v>3791</v>
       </c>
@@ -54642,7 +54642,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="1620" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1620" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1620" s="2" t="s">
         <v>3803</v>
       </c>
@@ -54798,7 +54798,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="1626" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1626" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1626" s="2" t="s">
         <v>3816</v>
       </c>
@@ -55734,7 +55734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="1662" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1662" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1662" s="2" t="s">
         <v>3880</v>
       </c>
@@ -55915,6 +55915,16 @@
       <c r="H1668" s="2">
         <v>80</v>
       </c>
+    </row>
+    <row r="1669" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1669" s="2"/>
+      <c r="B1669" s="2"/>
+      <c r="C1669" s="2"/>
+      <c r="D1669" s="2"/>
+      <c r="E1669" s="2"/>
+      <c r="F1669" s="2"/>
+      <c r="G1669" s="2"/>
+      <c r="H1669" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1668" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
